--- a/12515872.xlsx
+++ b/12515872.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MSC IT\Msc IT sem 3\PROGRAMMING IN PYTHON\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MSC IT\Msc IT sem 3\PROGRAMMING IN PYTHON\CAP776\CAP-776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{482F6AA9-4F46-4077-9238-1310B8456436}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBC3FAAE-DED1-48FC-93E6-C4E6CB81B7E6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="10110" windowHeight="4380" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1532,18 +1532,22 @@
       <c r="C17" s="14">
         <v>20</v>
       </c>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
+      <c r="D17" s="14">
+        <v>180</v>
+      </c>
+      <c r="E17" s="14">
+        <v>90</v>
+      </c>
       <c r="F17" s="14"/>
       <c r="G17" s="14"/>
       <c r="H17" s="14"/>
       <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v>380</v>
+        <v>650</v>
       </c>
       <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v>1060</v>
+        <v>790</v>
       </c>
       <c r="K17" s="16"/>
       <c r="L17" s="16"/>

--- a/12515872.xlsx
+++ b/12515872.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MSC IT\Msc IT sem 3\PROGRAMMING IN PYTHON\CAP776\CAP-776\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\MSC IT\Msc IT sem 3\PROGRAMMING IN PYTHON\CAP776\CAP-776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBC3FAAE-DED1-48FC-93E6-C4E6CB81B7E6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19A6308B-6875-40AB-9B98-F84FEAF7CE19}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="10110" windowHeight="4380" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="76">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -236,6 +236,24 @@
   </si>
   <si>
     <t>tired afterclasses</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>Had a good day</t>
+  </si>
+  <si>
+    <t>longest fitness time</t>
+  </si>
+  <si>
+    <t>fitness was good today</t>
+  </si>
+  <si>
+    <t>Learn a lot today at school</t>
   </si>
 </sst>
 </file>
@@ -1538,109 +1556,219 @@
       <c r="E17" s="14">
         <v>90</v>
       </c>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
+      <c r="F17" s="14">
+        <v>360</v>
+      </c>
+      <c r="G17" s="14">
+        <v>6</v>
+      </c>
+      <c r="H17" s="14">
+        <v>120</v>
+      </c>
       <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v>650</v>
+        <v>1130</v>
       </c>
       <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v>790</v>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+        <v>310</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="A18" s="13">
+        <v>46255</v>
+      </c>
+      <c r="B18" s="14">
+        <v>420</v>
+      </c>
+      <c r="C18" s="14">
+        <v>90</v>
+      </c>
+      <c r="D18" s="14">
+        <v>60</v>
+      </c>
+      <c r="E18" s="14">
+        <v>90</v>
+      </c>
+      <c r="F18" s="14">
+        <v>0</v>
+      </c>
+      <c r="G18" s="14">
+        <v>0</v>
+      </c>
+      <c r="H18" s="14">
+        <v>120</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>780</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
+        <v>660</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="A19" s="13">
+        <v>46256</v>
+      </c>
+      <c r="B19" s="14">
+        <v>420</v>
+      </c>
+      <c r="C19" s="14">
+        <v>60</v>
+      </c>
+      <c r="D19" s="14">
+        <v>60</v>
+      </c>
+      <c r="E19" s="14">
+        <v>0</v>
+      </c>
+      <c r="F19" s="14">
+        <v>0</v>
+      </c>
+      <c r="G19" s="14">
+        <v>0</v>
+      </c>
+      <c r="H19" s="14">
+        <v>0</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>540</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+        <v>900</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="A20" s="13">
+        <v>46257</v>
+      </c>
+      <c r="B20" s="14">
+        <v>420</v>
+      </c>
+      <c r="C20" s="14">
+        <v>60</v>
+      </c>
+      <c r="D20" s="14">
+        <v>90</v>
+      </c>
+      <c r="E20" s="14">
+        <v>0</v>
+      </c>
+      <c r="F20" s="14">
+        <v>0</v>
+      </c>
+      <c r="G20" s="14">
+        <v>0</v>
+      </c>
+      <c r="H20" s="14">
+        <v>0</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>570</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
+        <v>870</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+      <c r="A21" s="13">
+        <v>46258</v>
+      </c>
+      <c r="B21" s="14">
+        <v>270</v>
+      </c>
+      <c r="C21" s="14">
+        <v>30</v>
+      </c>
+      <c r="D21" s="14">
+        <v>180</v>
+      </c>
+      <c r="E21" s="14">
+        <v>120</v>
+      </c>
+      <c r="F21" s="14">
+        <v>360</v>
+      </c>
+      <c r="G21" s="14">
+        <v>6</v>
+      </c>
+      <c r="H21" s="14">
+        <v>120</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
+        <v>360</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="13"/>

--- a/12515872.xlsx
+++ b/12515872.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\MSC IT\Msc IT sem 3\PROGRAMMING IN PYTHON\CAP776\CAP-776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19A6308B-6875-40AB-9B98-F84FEAF7CE19}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD1E211D-3F6E-4C14-85F8-C873B07C3A33}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="10110" windowHeight="4380" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="82">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -254,6 +254,24 @@
   </si>
   <si>
     <t>Learn a lot today at school</t>
+  </si>
+  <si>
+    <t>Headache</t>
+  </si>
+  <si>
+    <t>Eye pain and fatigue</t>
+  </si>
+  <si>
+    <t>highly motivated</t>
+  </si>
+  <si>
+    <t>low motivation to study</t>
+  </si>
+  <si>
+    <t>Stressed</t>
+  </si>
+  <si>
+    <t>Very Unsatisfied</t>
   </si>
 </sst>
 </file>
@@ -1771,131 +1789,255 @@
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="A22" s="13">
+        <v>46259</v>
+      </c>
+      <c r="B22" s="14">
+        <v>300</v>
+      </c>
+      <c r="C22" s="14">
+        <v>30</v>
+      </c>
+      <c r="D22" s="14">
+        <v>60</v>
+      </c>
+      <c r="E22" s="14">
+        <v>120</v>
+      </c>
+      <c r="F22" s="14">
+        <v>300</v>
+      </c>
+      <c r="G22" s="14">
+        <v>5</v>
+      </c>
+      <c r="H22" s="14">
+        <v>60</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>870</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+        <v>570</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+      <c r="A23" s="13">
+        <v>46260</v>
+      </c>
+      <c r="B23" s="14">
+        <v>360</v>
+      </c>
+      <c r="C23" s="14">
+        <v>30</v>
+      </c>
+      <c r="D23" s="14">
+        <v>120</v>
+      </c>
+      <c r="E23" s="14">
+        <v>60</v>
+      </c>
+      <c r="F23" s="14">
+        <v>240</v>
+      </c>
+      <c r="G23" s="14">
+        <v>4</v>
+      </c>
+      <c r="H23" s="14">
+        <v>120</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
+        <v>510</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+      <c r="A24" s="13">
+        <v>46261</v>
+      </c>
+      <c r="B24" s="14">
+        <v>420</v>
+      </c>
+      <c r="C24" s="14">
+        <v>0</v>
+      </c>
+      <c r="D24" s="14">
+        <v>180</v>
+      </c>
+      <c r="E24" s="14">
+        <v>0</v>
+      </c>
+      <c r="F24" s="14">
+        <v>360</v>
+      </c>
+      <c r="G24" s="14">
+        <v>6</v>
+      </c>
+      <c r="H24" s="14">
+        <v>120</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
+        <v>360</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+      <c r="A25" s="13">
+        <v>46262</v>
+      </c>
+      <c r="B25" s="14">
+        <v>480</v>
+      </c>
+      <c r="C25" s="14">
+        <v>90</v>
+      </c>
+      <c r="D25" s="14">
+        <v>0</v>
+      </c>
+      <c r="E25" s="14">
+        <v>0</v>
+      </c>
+      <c r="F25" s="14">
+        <v>0</v>
+      </c>
+      <c r="G25" s="14">
+        <v>0</v>
+      </c>
+      <c r="H25" s="14">
+        <v>180</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>750</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+        <v>690</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A26" s="13">
+        <v>46263</v>
+      </c>
+      <c r="B26" s="14">
+        <v>420</v>
+      </c>
+      <c r="C26" s="14">
+        <v>0</v>
+      </c>
+      <c r="D26" s="14">
+        <v>180</v>
+      </c>
+      <c r="E26" s="14">
+        <v>0</v>
+      </c>
+      <c r="F26" s="14">
+        <v>0</v>
+      </c>
+      <c r="G26" s="14">
+        <v>0</v>
+      </c>
+      <c r="H26" s="14">
+        <v>0</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>600</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
+        <v>840</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
+      <c r="A27" s="13">
+        <v>46264</v>
+      </c>
+      <c r="B27" s="14">
+        <v>360</v>
+      </c>
       <c r="C27" s="14"/>
       <c r="D27" s="14"/>
       <c r="E27" s="14"/>
       <c r="F27" s="14"/>
       <c r="G27" s="14"/>
       <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>360</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>1080</v>
       </c>
       <c r="K27" s="16"/>
       <c r="L27" s="16"/>

--- a/12515872.xlsx
+++ b/12515872.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\MSC IT\Msc IT sem 3\PROGRAMMING IN PYTHON\CAP776\CAP-776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD1E211D-3F6E-4C14-85F8-C873B07C3A33}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AFB5FE8-874C-48C1-8754-4B4ECB841E0D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="10110" windowHeight="4380" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="85">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -272,6 +272,15 @@
   </si>
   <si>
     <t>Very Unsatisfied</t>
+  </si>
+  <si>
+    <t>mainly house cleaning and laundry</t>
+  </si>
+  <si>
+    <t>Heavily tired</t>
+  </si>
+  <si>
+    <t>Good day</t>
   </si>
 </sst>
 </file>
@@ -1115,7 +1124,7 @@
         <v>120</v>
       </c>
       <c r="F7" s="14">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="G7" s="14">
         <v>4</v>
@@ -1125,11 +1134,11 @@
       </c>
       <c r="I7" s="15">
         <f t="shared" si="0"/>
-        <v>1155</v>
+        <v>1115</v>
       </c>
       <c r="J7" s="15">
         <f t="shared" si="1"/>
-        <v>285</v>
+        <v>325</v>
       </c>
       <c r="K7" s="16" t="s">
         <v>49</v>
@@ -1161,7 +1170,7 @@
         <v>90</v>
       </c>
       <c r="F8" s="14">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="G8" s="14">
         <v>4</v>
@@ -1171,11 +1180,11 @@
       </c>
       <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v>980</v>
+        <v>940</v>
       </c>
       <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v>460</v>
+        <v>500</v>
       </c>
       <c r="K8" s="16" t="s">
         <v>58</v>
@@ -1207,7 +1216,7 @@
         <v>60</v>
       </c>
       <c r="F9" s="14">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="G9" s="14">
         <v>4</v>
@@ -1217,11 +1226,11 @@
       </c>
       <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v>950</v>
+        <v>910</v>
       </c>
       <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v>490</v>
+        <v>530</v>
       </c>
       <c r="K9" s="16" t="s">
         <v>61</v>
@@ -1253,7 +1262,7 @@
         <v>120</v>
       </c>
       <c r="F10" s="14">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="G10" s="14">
         <v>6</v>
@@ -1263,11 +1272,11 @@
       </c>
       <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v>1130</v>
+        <v>1070</v>
       </c>
       <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v>310</v>
+        <v>370</v>
       </c>
       <c r="K10" s="16" t="s">
         <v>49</v>
@@ -1437,7 +1446,7 @@
         <v>60</v>
       </c>
       <c r="F14" s="14">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="G14" s="14">
         <v>6</v>
@@ -1447,11 +1456,11 @@
       </c>
       <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v>985</v>
+        <v>925</v>
       </c>
       <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v>455</v>
+        <v>515</v>
       </c>
       <c r="K14" s="16" t="s">
         <v>49</v>
@@ -1483,7 +1492,7 @@
         <v>60</v>
       </c>
       <c r="F15" s="14">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G15" s="14">
         <v>5</v>
@@ -1493,11 +1502,11 @@
       </c>
       <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v>1010</v>
+        <v>960</v>
       </c>
       <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v>430</v>
+        <v>480</v>
       </c>
       <c r="K15" s="16" t="s">
         <v>58</v>
@@ -1529,7 +1538,7 @@
         <v>120</v>
       </c>
       <c r="F16" s="14">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="G16" s="14">
         <v>4</v>
@@ -1539,11 +1548,11 @@
       </c>
       <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v>990</v>
+        <v>950</v>
       </c>
       <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v>450</v>
+        <v>490</v>
       </c>
       <c r="K16" s="16" t="s">
         <v>61</v>
@@ -1575,7 +1584,7 @@
         <v>90</v>
       </c>
       <c r="F17" s="14">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="G17" s="14">
         <v>6</v>
@@ -1585,11 +1594,11 @@
       </c>
       <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v>1130</v>
+        <v>1070</v>
       </c>
       <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v>310</v>
+        <v>370</v>
       </c>
       <c r="K17" s="16" t="s">
         <v>49</v>
@@ -1759,7 +1768,7 @@
         <v>120</v>
       </c>
       <c r="F21" s="14">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="G21" s="14">
         <v>6</v>
@@ -1769,11 +1778,11 @@
       </c>
       <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v>1080</v>
+        <v>1020</v>
       </c>
       <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="K21" s="16" t="s">
         <v>70</v>
@@ -1805,7 +1814,7 @@
         <v>120</v>
       </c>
       <c r="F22" s="14">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G22" s="14">
         <v>5</v>
@@ -1815,11 +1824,11 @@
       </c>
       <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v>870</v>
+        <v>820</v>
       </c>
       <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v>570</v>
+        <v>620</v>
       </c>
       <c r="K22" s="16" t="s">
         <v>61</v>
@@ -1851,7 +1860,7 @@
         <v>60</v>
       </c>
       <c r="F23" s="14">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="G23" s="14">
         <v>4</v>
@@ -1861,11 +1870,11 @@
       </c>
       <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v>930</v>
+        <v>890</v>
       </c>
       <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v>510</v>
+        <v>550</v>
       </c>
       <c r="K23" s="16" t="s">
         <v>49</v>
@@ -1897,7 +1906,7 @@
         <v>0</v>
       </c>
       <c r="F24" s="14">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="G24" s="14">
         <v>6</v>
@@ -1907,11 +1916,11 @@
       </c>
       <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v>1080</v>
+        <v>1020</v>
       </c>
       <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="K24" s="16" t="s">
         <v>70</v>
@@ -2018,78 +2027,148 @@
         <v>79</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="13">
         <v>46264</v>
       </c>
       <c r="B27" s="14">
         <v>360</v>
       </c>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
+      <c r="C27" s="14">
+        <v>0</v>
+      </c>
+      <c r="D27" s="14">
+        <v>120</v>
+      </c>
+      <c r="E27" s="14">
+        <v>0</v>
+      </c>
+      <c r="F27" s="14">
+        <v>0</v>
+      </c>
+      <c r="G27" s="14">
+        <v>0</v>
+      </c>
+      <c r="H27" s="14">
+        <v>300</v>
+      </c>
       <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v>360</v>
+        <v>780</v>
       </c>
       <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v>1080</v>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
+        <v>660</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="A28" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B28" s="14">
+        <v>300</v>
+      </c>
+      <c r="C28" s="14">
+        <v>15</v>
+      </c>
+      <c r="D28" s="14">
+        <v>180</v>
+      </c>
+      <c r="E28" s="14">
+        <v>0</v>
+      </c>
+      <c r="F28" s="14">
+        <v>300</v>
+      </c>
+      <c r="G28" s="14">
+        <v>6</v>
+      </c>
+      <c r="H28" s="14">
+        <v>180</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>975</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
+        <v>465</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+      <c r="A29" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B29" s="14">
+        <v>300</v>
+      </c>
+      <c r="C29" s="14">
+        <v>15</v>
+      </c>
+      <c r="D29" s="14">
+        <v>60</v>
+      </c>
+      <c r="E29" s="14">
+        <v>120</v>
+      </c>
+      <c r="F29" s="14">
+        <v>250</v>
+      </c>
+      <c r="G29" s="14">
+        <v>5</v>
+      </c>
+      <c r="H29" s="14">
+        <v>250</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>995</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
+        <v>445</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="13"/>
+      <c r="A30" s="13">
+        <v>46267</v>
+      </c>
       <c r="B30" s="14"/>
       <c r="C30" s="14"/>
       <c r="D30" s="14"/>
@@ -2111,7 +2190,9 @@
       <c r="N30" s="17"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="13"/>
+      <c r="A31" s="13">
+        <v>46268</v>
+      </c>
       <c r="B31" s="14"/>
       <c r="C31" s="14"/>
       <c r="D31" s="14"/>
@@ -2133,7 +2214,9 @@
       <c r="N31" s="17"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="13"/>
+      <c r="A32" s="13">
+        <v>46269</v>
+      </c>
       <c r="B32" s="14"/>
       <c r="C32" s="14"/>
       <c r="D32" s="14"/>
@@ -2155,7 +2238,9 @@
       <c r="N32" s="17"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A33" s="13"/>
+      <c r="A33" s="13">
+        <v>46270</v>
+      </c>
       <c r="B33" s="14"/>
       <c r="C33" s="14"/>
       <c r="D33" s="14"/>
@@ -2177,7 +2262,9 @@
       <c r="N33" s="17"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A34" s="13"/>
+      <c r="A34" s="13">
+        <v>46271</v>
+      </c>
       <c r="B34" s="14"/>
       <c r="C34" s="14"/>
       <c r="D34" s="14"/>

--- a/12515872.xlsx
+++ b/12515872.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\MSC IT\Msc IT sem 3\PROGRAMMING IN PYTHON\CAP776\CAP-776\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MSC IT\Msc IT sem 3\PROGRAMMING IN PYTHON\CAP776\CAP-776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AFB5FE8-874C-48C1-8754-4B4ECB841E0D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6566FBF-1746-48ED-BC5B-C7FD71FD32E5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="10110" windowHeight="4380" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="87">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -281,6 +281,12 @@
   </si>
   <si>
     <t>Good day</t>
+  </si>
+  <si>
+    <t>Tooth pain</t>
+  </si>
+  <si>
+    <t>Severe Tooth pain</t>
   </si>
 </sst>
 </file>
@@ -2142,15 +2148,15 @@
         <v>5</v>
       </c>
       <c r="H29" s="14">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v>995</v>
+        <v>1045</v>
       </c>
       <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v>445</v>
+        <v>395</v>
       </c>
       <c r="K29" s="16" t="s">
         <v>49</v>
@@ -2169,73 +2175,135 @@
       <c r="A30" s="13">
         <v>46267</v>
       </c>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="B30" s="14">
+        <v>360</v>
+      </c>
+      <c r="C30" s="14">
+        <v>15</v>
+      </c>
+      <c r="D30" s="14">
+        <v>120</v>
+      </c>
+      <c r="E30" s="14">
+        <v>180</v>
+      </c>
+      <c r="F30" s="14">
+        <v>200</v>
+      </c>
+      <c r="G30" s="14">
+        <v>4</v>
+      </c>
+      <c r="H30" s="14">
+        <v>180</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>1055</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
+        <v>385</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="13">
         <v>46268</v>
       </c>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+      <c r="B31" s="14">
+        <v>300</v>
+      </c>
+      <c r="C31" s="14">
+        <v>0</v>
+      </c>
+      <c r="D31" s="14">
+        <v>180</v>
+      </c>
+      <c r="E31" s="14">
+        <v>180</v>
+      </c>
+      <c r="F31" s="14">
+        <v>300</v>
+      </c>
+      <c r="G31" s="14">
+        <v>6</v>
+      </c>
+      <c r="H31" s="14">
+        <v>300</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>1260</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
+        <v>180</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="13">
         <v>46269</v>
       </c>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
+      <c r="B32" s="14">
+        <v>420</v>
+      </c>
+      <c r="C32" s="14">
+        <v>0</v>
+      </c>
       <c r="D32" s="14"/>
       <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+      <c r="F32" s="14">
+        <v>0</v>
+      </c>
+      <c r="G32" s="14">
+        <v>0</v>
+      </c>
+      <c r="H32" s="14">
+        <v>240</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>660</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
+        <v>780</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="13">
@@ -2245,8 +2313,12 @@
       <c r="C33" s="14"/>
       <c r="D33" s="14"/>
       <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
+      <c r="F33" s="14">
+        <v>0</v>
+      </c>
+      <c r="G33" s="14">
+        <v>0</v>
+      </c>
       <c r="H33" s="14"/>
       <c r="I33" s="15" t="str">
         <f t="shared" si="0"/>
@@ -2269,8 +2341,12 @@
       <c r="C34" s="14"/>
       <c r="D34" s="14"/>
       <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
+      <c r="F34" s="14">
+        <v>0</v>
+      </c>
+      <c r="G34" s="14">
+        <v>0</v>
+      </c>
       <c r="H34" s="14"/>
       <c r="I34" s="15" t="str">
         <f t="shared" si="0"/>
